--- a/goods.xlsx
+++ b/goods.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="296">
   <si>
     <t>成分</t>
   </si>
@@ -685,6 +685,9 @@
     <t>68410a714b530700010cc0ca#5</t>
   </si>
   <si>
+    <t>净重：30斤</t>
+  </si>
+  <si>
     <t>693d54fb8b11d10001911111</t>
   </si>
   <si>
@@ -772,6 +775,9 @@
     <t>68c7680f24f1f80001210ae5</t>
   </si>
   <si>
+    <t>68c7680f24f1f80001210ae2#2</t>
+  </si>
+  <si>
     <t>673c16865ce03300019e43b7</t>
   </si>
   <si>
@@ -794,6 +800,18 @@
   </si>
   <si>
     <t>69055a5f9de01f0001185cf9</t>
+  </si>
+  <si>
+    <t>成分：芡实</t>
+  </si>
+  <si>
+    <t>产地：广东肇庆</t>
+  </si>
+  <si>
+    <t>等级：精选开边</t>
+  </si>
+  <si>
+    <t>22222222222fff2</t>
   </si>
   <si>
     <t>69226c4b6ea74e0001bd2408</t>
@@ -1527,7 +1545,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1543,8 +1561,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1857,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="32.75" customWidth="1"/>
@@ -3884,7 +3908,7 @@
         <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="D79" t="s">
         <v>16</v>
@@ -3893,7 +3917,7 @@
         <v>116</v>
       </c>
       <c r="G79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H79" t="s">
         <v>31</v>
@@ -3905,7 +3929,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
@@ -3917,24 +3941,24 @@
         <v>16</v>
       </c>
       <c r="E80" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G80" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H80" t="s">
         <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
@@ -3949,7 +3973,7 @@
         <v>147</v>
       </c>
       <c r="G81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H81" t="s">
         <v>150</v>
@@ -3975,7 +3999,7 @@
         <v>46</v>
       </c>
       <c r="G82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H82" t="s">
         <v>52</v>
@@ -3984,12 +4008,12 @@
         <v>53</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
@@ -4004,13 +4028,13 @@
         <v>76</v>
       </c>
       <c r="G83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H83" t="s">
         <v>19</v>
       </c>
       <c r="I83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -4030,7 +4054,7 @@
         <v>46</v>
       </c>
       <c r="G84" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H84" t="s">
         <v>52</v>
@@ -4039,18 +4063,18 @@
         <v>53</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D85" t="s">
         <v>16</v>
@@ -4059,7 +4083,7 @@
         <v>71</v>
       </c>
       <c r="G85" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H85" t="s">
         <v>31</v>
@@ -4085,7 +4109,7 @@
         <v>116</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H86" t="s">
         <v>31</v>
@@ -4111,7 +4135,7 @@
         <v>29</v>
       </c>
       <c r="G87" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H87" t="s">
         <v>31</v>
@@ -4137,7 +4161,7 @@
         <v>29</v>
       </c>
       <c r="G88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H88" t="s">
         <v>31</v>
@@ -4148,7 +4172,7 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B89" t="s">
         <v>14</v>
@@ -4160,21 +4184,21 @@
         <v>16</v>
       </c>
       <c r="E89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H89" t="s">
         <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B90" t="s">
         <v>14</v>
@@ -4186,24 +4210,24 @@
         <v>16</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B91" t="s">
         <v>14</v>
@@ -4215,24 +4239,24 @@
         <v>16</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G91" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
@@ -4244,19 +4268,22 @@
         <v>16</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="J92" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4276,7 +4303,7 @@
         <v>17</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H93" t="s">
         <v>19</v>
@@ -4287,7 +4314,7 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
@@ -4299,24 +4326,24 @@
         <v>16</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H94" t="s">
         <v>31</v>
       </c>
       <c r="I94" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
@@ -4331,16 +4358,16 @@
         <v>136</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H95" t="s">
         <v>31</v>
       </c>
       <c r="I95" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -4360,7 +4387,7 @@
         <v>101</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H96" t="s">
         <v>31</v>
@@ -4371,7 +4398,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B97" t="s">
         <v>14</v>
@@ -4386,16 +4413,16 @@
         <v>136</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H97" t="s">
         <v>31</v>
       </c>
       <c r="I97" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4415,10 +4442,10 @@
         <v>83</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H98" t="s">
         <v>31</v>
@@ -4429,36 +4456,39 @@
     </row>
     <row r="99" customFormat="1" spans="1:10">
       <c r="A99" t="s">
+        <v>257</v>
+      </c>
+      <c r="B99" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" t="s">
+        <v>258</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H99" t="s">
+        <v>31</v>
+      </c>
+      <c r="I99" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:10">
+      <c r="A100" t="s">
         <v>120</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>121</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" t="s">
-        <v>16</v>
-      </c>
-      <c r="E99" t="s">
-        <v>116</v>
-      </c>
-      <c r="G99" t="s">
-        <v>255</v>
-      </c>
-      <c r="H99" t="s">
-        <v>31</v>
-      </c>
-      <c r="I99" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="100" customFormat="1" ht="17" customHeight="1" spans="1:10">
-      <c r="A100" t="s">
-        <v>89</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
       </c>
       <c r="C100" t="s">
         <v>21</v>
@@ -4467,36 +4497,36 @@
         <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>256</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>257</v>
+        <v>116</v>
+      </c>
+      <c r="G100" t="s">
+        <v>261</v>
       </c>
       <c r="H100" t="s">
         <v>31</v>
       </c>
       <c r="I100" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A101" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="B101" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
         <v>16</v>
       </c>
       <c r="E101" t="s">
-        <v>256</v>
-      </c>
-      <c r="G101" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="H101" t="s">
         <v>31</v>
@@ -4504,265 +4534,262 @@
       <c r="I101" t="s">
         <v>93</v>
       </c>
-      <c r="J101" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:10">
+    </row>
+    <row r="102" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A102" t="s">
+        <v>264</v>
+      </c>
+      <c r="B102" t="s">
+        <v>265</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>262</v>
+      </c>
+      <c r="G102" t="s">
+        <v>266</v>
+      </c>
+      <c r="H102" t="s">
+        <v>31</v>
+      </c>
+      <c r="I102" t="s">
+        <v>93</v>
+      </c>
+      <c r="J102" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:10">
+      <c r="A103" t="s">
         <v>120</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>123</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" t="s">
         <v>21</v>
       </c>
-      <c r="D102" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
         <v>116</v>
       </c>
-      <c r="G102" t="s">
-        <v>262</v>
-      </c>
-      <c r="H102" t="s">
-        <v>31</v>
-      </c>
-      <c r="I102" t="s">
+      <c r="G103" t="s">
+        <v>268</v>
+      </c>
+      <c r="H103" t="s">
+        <v>31</v>
+      </c>
+      <c r="I103" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1" spans="1:10">
-      <c r="A103" t="s">
+    <row r="104" ht="18" customHeight="1" spans="1:10">
+      <c r="A104" t="s">
         <v>166</v>
       </c>
-      <c r="B103" t="s">
-        <v>14</v>
-      </c>
-      <c r="C103" t="s">
-        <v>263</v>
-      </c>
-      <c r="D103" t="s">
-        <v>16</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
         <v>167</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F104" t="s">
         <v>168</v>
       </c>
-      <c r="G103" t="s">
-        <v>264</v>
-      </c>
-      <c r="H103" t="s">
-        <v>31</v>
-      </c>
-      <c r="I103" t="s">
+      <c r="G104" t="s">
+        <v>270</v>
+      </c>
+      <c r="H104" t="s">
+        <v>31</v>
+      </c>
+      <c r="I104" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" t="s">
-        <v>265</v>
-      </c>
-      <c r="B104" t="s">
-        <v>14</v>
-      </c>
-      <c r="C104" t="s">
-        <v>146</v>
-      </c>
-      <c r="D104" t="s">
-        <v>16</v>
-      </c>
-      <c r="E104" t="s">
-        <v>147</v>
-      </c>
-      <c r="F104" t="s">
-        <v>266</v>
-      </c>
-      <c r="G104" t="s">
-        <v>267</v>
-      </c>
-      <c r="H104" t="s">
-        <v>150</v>
-      </c>
-      <c r="I104" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>50</v>
+        <v>271</v>
       </c>
       <c r="B105" t="s">
         <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
         <v>16</v>
       </c>
       <c r="E105" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="F105" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G105" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="I105" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
       </c>
       <c r="E106" t="s">
-        <v>29</v>
+        <v>46</v>
+      </c>
+      <c r="F106" t="s">
+        <v>274</v>
       </c>
       <c r="G106" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H106" t="s">
         <v>31</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>271</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" t="s">
+        <v>276</v>
+      </c>
+      <c r="H107" t="s">
+        <v>31</v>
+      </c>
+      <c r="I107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>277</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" t="s">
         <v>146</v>
       </c>
-      <c r="D107" t="s">
-        <v>16</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
         <v>147</v>
-      </c>
-      <c r="F107" t="s">
-        <v>148</v>
-      </c>
-      <c r="G107" t="s">
-        <v>272</v>
-      </c>
-      <c r="H107" t="s">
-        <v>150</v>
-      </c>
-      <c r="I107" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B108" t="s">
-        <v>121</v>
-      </c>
-      <c r="C108" t="s">
-        <v>37</v>
-      </c>
-      <c r="D108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E108" t="s">
-        <v>116</v>
       </c>
       <c r="F108" t="s">
         <v>148</v>
       </c>
       <c r="G108" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="I108" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" t="s">
+        <v>121</v>
+      </c>
+      <c r="C109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
+        <v>116</v>
+      </c>
+      <c r="F109" t="s">
+        <v>148</v>
+      </c>
+      <c r="G109" t="s">
+        <v>279</v>
+      </c>
+      <c r="H109" t="s">
+        <v>31</v>
+      </c>
+      <c r="I109" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
-      <c r="A109" t="s">
-        <v>271</v>
-      </c>
-      <c r="B109" t="s">
-        <v>14</v>
-      </c>
-      <c r="C109" t="s">
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>277</v>
+      </c>
+      <c r="B110" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" t="s">
         <v>15</v>
       </c>
-      <c r="D109" t="s">
-        <v>16</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
         <v>147</v>
       </c>
-      <c r="G109" t="s">
-        <v>274</v>
-      </c>
-      <c r="H109" t="s">
+      <c r="G110" t="s">
+        <v>280</v>
+      </c>
+      <c r="H110" t="s">
         <v>150</v>
       </c>
-      <c r="I109" t="s">
+      <c r="I110" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="110" customFormat="1" spans="1:10">
-      <c r="A110" t="s">
-        <v>275</v>
-      </c>
-      <c r="B110" t="s">
-        <v>14</v>
-      </c>
-      <c r="C110" t="s">
-        <v>37</v>
-      </c>
-      <c r="D110" t="s">
-        <v>16</v>
-      </c>
-      <c r="E110" t="s">
-        <v>276</v>
-      </c>
-      <c r="F110" t="s">
-        <v>277</v>
-      </c>
-      <c r="G110" t="s">
-        <v>278</v>
-      </c>
-      <c r="H110" t="s">
-        <v>31</v>
-      </c>
-      <c r="I110" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:10">
       <c r="A111" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B111" t="s">
         <v>14</v>
@@ -4774,82 +4801,137 @@
         <v>16</v>
       </c>
       <c r="E111" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F111" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G111" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H111" t="s">
         <v>31</v>
       </c>
       <c r="I111" t="s">
-        <v>279</v>
-      </c>
-      <c r="J111" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:10">
       <c r="A112" t="s">
+        <v>281</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" t="s">
         <v>282</v>
       </c>
-      <c r="B112" t="s">
-        <v>14</v>
-      </c>
-      <c r="C112" t="s">
-        <v>191</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>283</v>
       </c>
-      <c r="E112" t="s">
-        <v>284</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
+        <v>286</v>
+      </c>
+      <c r="H112" t="s">
+        <v>31</v>
+      </c>
+      <c r="I112" t="s">
         <v>285</v>
       </c>
-      <c r="G112">
-        <v>89789</v>
-      </c>
-      <c r="H112" t="s">
-        <v>31</v>
-      </c>
-      <c r="I112" t="s">
-        <v>286</v>
+      <c r="J112" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:10">
       <c r="A113" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B113" t="s">
         <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>288</v>
+        <v>191</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>289</v>
       </c>
       <c r="E113" t="s">
+        <v>290</v>
+      </c>
+      <c r="F113" t="s">
+        <v>291</v>
+      </c>
+      <c r="G113">
+        <v>89789</v>
+      </c>
+      <c r="H113" t="s">
+        <v>31</v>
+      </c>
+      <c r="I113" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" spans="1:10">
+      <c r="A114" t="s">
+        <v>293</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>294</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
         <v>116</v>
       </c>
-      <c r="F113" t="s">
-        <v>285</v>
-      </c>
-      <c r="G113">
+      <c r="F114" t="s">
+        <v>291</v>
+      </c>
+      <c r="G114">
         <v>11223311223</v>
       </c>
-      <c r="H113" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" t="s">
-        <v>289</v>
-      </c>
-      <c r="J113" s="1"/>
+      <c r="H114" t="s">
+        <v>31</v>
+      </c>
+      <c r="I114" t="s">
+        <v>295</v>
+      </c>
+      <c r="J114" s="1"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>121</v>
+      </c>
+      <c r="C115" t="s">
+        <v>218</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>116</v>
+      </c>
+      <c r="G115" t="s">
+        <v>122</v>
+      </c>
+      <c r="H115" t="s">
+        <v>31</v>
+      </c>
+      <c r="I115" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A2:J67">

--- a/goods.xlsx
+++ b/goods.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="300">
   <si>
     <t>成分</t>
   </si>
@@ -163,6 +163,9 @@
     <t>6735b2c8ef36300001ac6c19#2</t>
   </si>
   <si>
+    <t>6a0e56751373950001ff2729</t>
+  </si>
+  <si>
     <t>6735b2c8ef36300001ac6c19</t>
   </si>
   <si>
@@ -917,6 +920,15 @@
   </si>
   <si>
     <t>lzx</t>
+  </si>
+  <si>
+    <t>成分：无花果</t>
+  </si>
+  <si>
+    <t>11111111ac79f0001afb730</t>
+  </si>
+  <si>
+    <t>zdy</t>
   </si>
 </sst>
 </file>
@@ -1545,11 +1557,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1881,7 +1896,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="32.75" customWidth="1"/>
@@ -2149,7 +2164,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" customFormat="1" spans="1:10">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -2157,7 +2172,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -2165,7 +2180,7 @@
       <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H11" t="s">
@@ -2174,68 +2189,66 @@
       <c r="I11" t="s">
         <v>42</v>
       </c>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="F12" t="s">
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
         <v>47</v>
       </c>
-      <c r="G12" t="s">
+      <c r="F13" t="s">
         <v>48</v>
       </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="G13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" ht="15.75" spans="1:10">
-      <c r="A13" t="s">
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
+    </row>
+    <row r="14" ht="15.75" spans="1:10">
+      <c r="A14" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>50</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -2247,47 +2260,50 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="H14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -2299,21 +2315,21 @@
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -2325,7 +2341,7 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
         <v>62</v>
@@ -2334,15 +2350,15 @@
         <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -2351,90 +2367,90 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>58</v>
       </c>
       <c r="G19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" t="s">
         <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" t="s">
         <v>74</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
@@ -2443,33 +2459,33 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s">
         <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
         <v>81</v>
@@ -2478,44 +2494,38 @@
         <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s">
         <v>82</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" t="s">
-        <v>85</v>
-      </c>
       <c r="H24" t="s">
         <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -2527,120 +2537,126 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25">
-        <v>12121212</v>
+        <v>85</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
       </c>
       <c r="H25" t="s">
         <v>31</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="J25" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" t="s">
-        <v>88</v>
+        <v>85</v>
+      </c>
+      <c r="G26">
+        <v>12121212</v>
       </c>
       <c r="H26" t="s">
         <v>31</v>
       </c>
       <c r="I26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" t="s">
         <v>89</v>
       </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>91</v>
-      </c>
-      <c r="G27" t="s">
-        <v>92</v>
-      </c>
       <c r="H27" t="s">
         <v>31</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
       </c>
       <c r="D28" t="s">
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" t="s">
+        <v>94</v>
+      </c>
+      <c r="J28" t="s">
         <v>95</v>
-      </c>
-      <c r="H28" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>96</v>
@@ -2649,203 +2665,203 @@
         <v>31</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C30" t="s">
+      <c r="H30" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:10">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
         <v>37</v>
       </c>
-      <c r="D30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H30" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="1" t="s">
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="H31" t="s">
         <v>31</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H32" t="s">
         <v>31</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="1" t="s">
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" t="s">
-        <v>93</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="C34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" t="s">
         <v>109</v>
-      </c>
-      <c r="B34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G34" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" t="s">
         <v>114</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" t="s">
-        <v>117</v>
-      </c>
-      <c r="H35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" t="s">
         <v>120</v>
-      </c>
-      <c r="B36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-      <c r="H36" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
@@ -2854,24 +2870,24 @@
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
         <v>124</v>
-      </c>
-      <c r="H37" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>125</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
@@ -2880,24 +2896,24 @@
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G38" t="s">
+        <v>125</v>
+      </c>
+      <c r="H38" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>126</v>
-      </c>
-      <c r="H38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" t="s">
-        <v>115</v>
       </c>
       <c r="C39" t="s">
         <v>37</v>
@@ -2906,53 +2922,50 @@
         <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
-      </c>
-      <c r="G39" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" t="s">
         <v>127</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
       </c>
       <c r="I39" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G40" t="s">
-        <v>129</v>
-      </c>
       <c r="H40" t="s">
         <v>31</v>
       </c>
       <c r="I40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -2961,24 +2974,27 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" t="s">
+        <v>129</v>
+      </c>
+      <c r="G41" t="s">
         <v>130</v>
       </c>
       <c r="H41" t="s">
         <v>31</v>
       </c>
       <c r="I41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -2987,355 +3003,352 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>131</v>
       </c>
       <c r="H42" t="s">
         <v>31</v>
       </c>
       <c r="I42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" t="s">
         <v>132</v>
       </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="H43" t="s">
         <v>31</v>
       </c>
       <c r="I43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B44" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" t="s">
-        <v>136</v>
-      </c>
-      <c r="G44" t="s">
-        <v>137</v>
-      </c>
       <c r="H44" t="s">
         <v>31</v>
       </c>
       <c r="I44" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D45" t="s">
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G45" t="s">
+        <v>138</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" t="s">
         <v>139</v>
-      </c>
-      <c r="H45" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" t="s">
         <v>141</v>
-      </c>
-      <c r="B46" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" t="s">
-        <v>142</v>
-      </c>
-      <c r="H46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I46" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" t="s">
+        <v>143</v>
+      </c>
+      <c r="H47" t="s">
+        <v>144</v>
+      </c>
+      <c r="I47" t="s">
         <v>145</v>
-      </c>
-      <c r="B47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" t="s">
-        <v>146</v>
-      </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" t="s">
-        <v>147</v>
-      </c>
-      <c r="F47" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" t="s">
-        <v>149</v>
-      </c>
-      <c r="H47" t="s">
-        <v>150</v>
-      </c>
-      <c r="I47" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D48" t="s">
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="F48" t="s">
+        <v>149</v>
       </c>
       <c r="G48" t="s">
+        <v>150</v>
+      </c>
+      <c r="H48" t="s">
+        <v>151</v>
+      </c>
+      <c r="I48" t="s">
         <v>152</v>
-      </c>
-      <c r="H48" t="s">
-        <v>150</v>
-      </c>
-      <c r="I48" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G49" t="s">
         <v>153</v>
       </c>
       <c r="H49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D50" t="s">
         <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
         <v>154</v>
       </c>
       <c r="H50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="s">
+        <v>148</v>
+      </c>
+      <c r="G51" t="s">
         <v>155</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G51" t="s">
-        <v>157</v>
-      </c>
       <c r="H51" t="s">
-        <v>52</v>
-      </c>
-      <c r="J51" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="I51" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>155</v>
-      </c>
-      <c r="B52" s="4" t="s">
         <v>156</v>
       </c>
+      <c r="B52" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="G52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H52" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="J52" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>159</v>
+        <v>156</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H53" t="s">
-        <v>52</v>
-      </c>
-      <c r="I53" t="s">
-        <v>161</v>
-      </c>
-      <c r="J53" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
+        <v>160</v>
+      </c>
+      <c r="G54" t="s">
+        <v>161</v>
+      </c>
+      <c r="H54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I54" t="s">
+        <v>162</v>
+      </c>
+      <c r="J54" t="s">
         <v>163</v>
-      </c>
-      <c r="G54" t="s">
-        <v>164</v>
-      </c>
-      <c r="H54" t="s">
-        <v>52</v>
-      </c>
-      <c r="I54" t="s">
-        <v>161</v>
-      </c>
-      <c r="J54" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" t="s">
+        <v>53</v>
+      </c>
+      <c r="I55" t="s">
+        <v>162</v>
+      </c>
+      <c r="J55" t="s">
         <v>166</v>
-      </c>
-      <c r="B55" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" t="s">
-        <v>16</v>
-      </c>
-      <c r="E55" t="s">
-        <v>167</v>
-      </c>
-      <c r="F55" t="s">
-        <v>168</v>
-      </c>
-      <c r="G55" t="s">
-        <v>169</v>
-      </c>
-      <c r="H55" t="s">
-        <v>52</v>
-      </c>
-      <c r="I55" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D56" t="s">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F56" t="s">
-        <v>168</v>
-      </c>
-      <c r="G56" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G56" t="s">
         <v>170</v>
       </c>
       <c r="H56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I56" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -3347,545 +3360,547 @@
         <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>173</v>
-      </c>
-      <c r="G57" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="F57" t="s">
+        <v>169</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="H57" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="I57" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
+        <v>174</v>
+      </c>
+      <c r="G58" t="s">
+        <v>175</v>
+      </c>
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
         <v>176</v>
-      </c>
-      <c r="B58" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58" t="s">
-        <v>147</v>
-      </c>
-      <c r="G58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H58" t="s">
-        <v>150</v>
-      </c>
-      <c r="I58" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D59" t="s">
         <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
-      </c>
-      <c r="F59" t="s">
         <v>148</v>
       </c>
       <c r="G59" t="s">
         <v>178</v>
       </c>
       <c r="H59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
         <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="F60" t="s">
+        <v>149</v>
       </c>
       <c r="G60" t="s">
         <v>179</v>
       </c>
       <c r="H60" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D61" t="s">
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G61" t="s">
         <v>180</v>
       </c>
       <c r="H61" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" t="s">
+        <v>148</v>
+      </c>
+      <c r="G62" t="s">
         <v>181</v>
       </c>
-      <c r="B62" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" t="s">
-        <v>147</v>
-      </c>
-      <c r="G62" t="s">
-        <v>182</v>
-      </c>
       <c r="H62" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I62" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>148</v>
+      </c>
+      <c r="G63" t="s">
         <v>183</v>
       </c>
-      <c r="B63" t="s">
-        <v>14</v>
-      </c>
-      <c r="C63" t="s">
-        <v>146</v>
-      </c>
-      <c r="D63" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" t="s">
-        <v>173</v>
-      </c>
-      <c r="F63" t="s">
-        <v>184</v>
-      </c>
-      <c r="G63" t="s">
-        <v>185</v>
-      </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="I63" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
       </c>
       <c r="C64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
+        <v>174</v>
+      </c>
+      <c r="F64" t="s">
+        <v>185</v>
+      </c>
+      <c r="G64" t="s">
+        <v>186</v>
+      </c>
+      <c r="H64" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" t="s">
         <v>187</v>
-      </c>
-      <c r="D64" t="s">
-        <v>16</v>
-      </c>
-      <c r="E64" t="s">
-        <v>173</v>
-      </c>
-      <c r="F64" t="s">
-        <v>184</v>
-      </c>
-      <c r="G64" t="s">
-        <v>188</v>
-      </c>
-      <c r="H64" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" t="s">
-        <v>186</v>
-      </c>
-      <c r="J64" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="D65" t="s">
         <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G65" t="s">
+        <v>189</v>
+      </c>
+      <c r="H65" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" t="s">
+        <v>187</v>
+      </c>
+      <c r="J65" t="s">
         <v>190</v>
-      </c>
-      <c r="H65" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
       </c>
       <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" t="s">
+        <v>174</v>
+      </c>
+      <c r="F66" t="s">
+        <v>185</v>
+      </c>
+      <c r="G66" t="s">
         <v>191</v>
       </c>
-      <c r="D66" t="s">
-        <v>16</v>
-      </c>
-      <c r="E66" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="H66" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
         <v>184</v>
       </c>
-      <c r="G66" t="s">
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
         <v>192</v>
       </c>
-      <c r="H66" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="1" t="s">
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
+        <v>174</v>
+      </c>
+      <c r="F67" t="s">
+        <v>185</v>
+      </c>
+      <c r="G67" t="s">
         <v>193</v>
       </c>
-      <c r="B67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D67" t="s">
-        <v>16</v>
-      </c>
-      <c r="E67" t="s">
-        <v>173</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="H67" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G67" t="s">
+      <c r="B68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
+        <v>174</v>
+      </c>
+      <c r="F68" t="s">
         <v>195</v>
       </c>
-      <c r="H67" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>183</v>
-      </c>
-      <c r="B68" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="G68" t="s">
+        <v>196</v>
+      </c>
+      <c r="H68" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
         <v>21</v>
       </c>
-      <c r="D68" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" t="s">
-        <v>173</v>
-      </c>
-      <c r="F68" t="s">
-        <v>184</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H68" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="1" t="s">
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>174</v>
+      </c>
+      <c r="F69" t="s">
+        <v>185</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="1" t="s">
+      <c r="H69" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D69" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" t="s">
-        <v>173</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H69" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>183</v>
-      </c>
-      <c r="B70" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" t="s">
-        <v>146</v>
-      </c>
-      <c r="D70" t="s">
-        <v>16</v>
-      </c>
-      <c r="E70" t="s">
-        <v>173</v>
-      </c>
-      <c r="F70" t="s">
-        <v>184</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="G70" s="1" t="s">
         <v>200</v>
       </c>
       <c r="H70" t="s">
         <v>31</v>
       </c>
       <c r="I70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
-        <v>184</v>
-      </c>
-      <c r="G71">
-        <v>123123123</v>
+        <v>185</v>
+      </c>
+      <c r="G71" t="s">
+        <v>201</v>
       </c>
       <c r="H71" t="s">
         <v>31</v>
       </c>
       <c r="I71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>201</v>
-      </c>
-      <c r="G72" t="s">
-        <v>202</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>203</v>
+        <v>184</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
+        <v>185</v>
+      </c>
+      <c r="G72">
+        <v>123123123</v>
+      </c>
+      <c r="H72" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
+        <v>202</v>
+      </c>
+      <c r="G73" t="s">
+        <v>203</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G73" t="s">
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
         <v>205</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="G74" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G74" s="1" t="s">
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
-        <v>120</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="J75" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C75" t="s">
-        <v>37</v>
-      </c>
-      <c r="D75" t="s">
-        <v>16</v>
-      </c>
-      <c r="E75" t="s">
-        <v>116</v>
-      </c>
-      <c r="G75" t="s">
-        <v>211</v>
-      </c>
-      <c r="H75" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C76" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" t="s">
         <v>212</v>
       </c>
-      <c r="D76" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" t="s">
-        <v>116</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>121</v>
+      </c>
+      <c r="B77" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" t="s">
         <v>213</v>
       </c>
-      <c r="H76" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" t="s">
-        <v>118</v>
-      </c>
-      <c r="J76" s="1" t="s">
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="77" customFormat="1" spans="1:10">
-      <c r="A77" t="s">
-        <v>120</v>
-      </c>
-      <c r="B77" t="s">
-        <v>210</v>
-      </c>
-      <c r="C77" t="s">
-        <v>132</v>
-      </c>
-      <c r="D77" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" t="s">
-        <v>116</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" t="s">
+        <v>119</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H77" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" t="s">
-        <v>118</v>
-      </c>
-      <c r="J77" s="1"/>
     </row>
     <row r="78" customFormat="1" spans="1:10">
       <c r="A78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
         <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G78" t="s">
         <v>216</v>
@@ -3894,126 +3909,124 @@
         <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>118</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="J78" s="1"/>
     </row>
     <row r="79" customFormat="1" spans="1:10">
       <c r="A79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C79" t="s">
+        <v>213</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>117</v>
+      </c>
+      <c r="G79" t="s">
+        <v>217</v>
+      </c>
+      <c r="H79" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" t="s">
+        <v>119</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" t="s">
-        <v>116</v>
-      </c>
-      <c r="G79" t="s">
+    </row>
+    <row r="80" customFormat="1" spans="1:10">
+      <c r="A80" t="s">
+        <v>121</v>
+      </c>
+      <c r="B80" t="s">
+        <v>211</v>
+      </c>
+      <c r="C80" t="s">
         <v>219</v>
       </c>
-      <c r="H79" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" t="s">
-        <v>118</v>
-      </c>
-      <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" t="s">
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
+        <v>117</v>
+      </c>
+      <c r="G80" t="s">
         <v>220</v>
       </c>
-      <c r="B80" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" t="s">
-        <v>16</v>
-      </c>
-      <c r="E80" t="s">
-        <v>221</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G80" t="s">
-        <v>223</v>
-      </c>
       <c r="H80" t="s">
         <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>224</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
+        <v>221</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
+        <v>222</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G81" t="s">
+        <v>224</v>
+      </c>
+      <c r="H81" t="s">
+        <v>31</v>
+      </c>
+      <c r="I81" t="s">
         <v>225</v>
       </c>
-      <c r="B81" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" t="s">
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>226</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
         <v>21</v>
       </c>
-      <c r="D81" t="s">
-        <v>16</v>
-      </c>
-      <c r="E81" t="s">
-        <v>147</v>
-      </c>
-      <c r="G81" t="s">
-        <v>226</v>
-      </c>
-      <c r="H81" t="s">
-        <v>150</v>
-      </c>
-      <c r="I81" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" spans="1:10">
-      <c r="A82" t="s">
-        <v>50</v>
-      </c>
-      <c r="B82" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" t="s">
-        <v>37</v>
-      </c>
       <c r="D82" t="s">
         <v>16</v>
       </c>
       <c r="E82" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="G82" t="s">
         <v>227</v>
       </c>
       <c r="H82" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" spans="1:10">
       <c r="A83" t="s">
-        <v>229</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
@@ -4025,21 +4038,24 @@
         <v>16</v>
       </c>
       <c r="E83" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G83" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H83" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="I83" t="s">
-        <v>231</v>
+        <v>54</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
@@ -4051,97 +4067,97 @@
         <v>16</v>
       </c>
       <c r="E84" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s">
+        <v>231</v>
+      </c>
+      <c r="H84" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" t="s">
         <v>232</v>
-      </c>
-      <c r="H84" t="s">
-        <v>52</v>
-      </c>
-      <c r="I84" t="s">
-        <v>53</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" t="s">
+        <v>47</v>
+      </c>
+      <c r="G85" t="s">
+        <v>233</v>
+      </c>
+      <c r="H85" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" t="s">
+        <v>54</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B85" t="s">
-        <v>235</v>
-      </c>
-      <c r="C85" t="s">
-        <v>236</v>
-      </c>
-      <c r="D85" t="s">
-        <v>16</v>
-      </c>
-      <c r="E85" t="s">
-        <v>71</v>
-      </c>
-      <c r="G85" t="s">
-        <v>237</v>
-      </c>
-      <c r="H85" t="s">
-        <v>31</v>
-      </c>
-      <c r="I85" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="C86" t="s">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="D86" t="s">
         <v>16</v>
       </c>
       <c r="E86" t="s">
-        <v>116</v>
-      </c>
-      <c r="G86" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G86" t="s">
         <v>238</v>
       </c>
       <c r="H86" t="s">
         <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
-      </c>
-      <c r="G87" t="s">
+        <v>117</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>239</v>
       </c>
       <c r="H87" t="s">
         <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -4161,7 +4177,7 @@
         <v>29</v>
       </c>
       <c r="G88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H88" t="s">
         <v>31</v>
@@ -4172,106 +4188,103 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>146</v>
+        <v>33</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
       </c>
       <c r="D89" t="s">
         <v>16</v>
       </c>
       <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" t="s">
+        <v>240</v>
+      </c>
+      <c r="H89" t="s">
+        <v>31</v>
+      </c>
+      <c r="I89" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
         <v>221</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H89" t="s">
-        <v>31</v>
-      </c>
-      <c r="I89" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="1" t="s">
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>222</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B90" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" t="s">
-        <v>16</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>245</v>
+      <c r="H90" t="s">
+        <v>31</v>
+      </c>
+      <c r="I90" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B91" t="s">
         <v>14</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G91" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>247</v>
@@ -4280,15 +4293,12 @@
         <v>31</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J92" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>24</v>
+      <c r="A93" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
@@ -4299,51 +4309,54 @@
       <c r="D93" t="s">
         <v>16</v>
       </c>
-      <c r="E93" t="s">
-        <v>17</v>
+      <c r="E93" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J93" t="s">
         <v>249</v>
-      </c>
-      <c r="H93" t="s">
-        <v>19</v>
-      </c>
-      <c r="I93" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>222</v>
+      <c r="E94" t="s">
+        <v>17</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>250</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I94" t="s">
-        <v>224</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
@@ -4355,10 +4368,10 @@
         <v>16</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>251</v>
@@ -4367,15 +4380,15 @@
         <v>31</v>
       </c>
       <c r="I95" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>100</v>
+      <c r="A96" t="s">
+        <v>221</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>21</v>
@@ -4384,7 +4397,10 @@
         <v>16</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>252</v>
@@ -4393,15 +4409,15 @@
         <v>31</v>
       </c>
       <c r="I96" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B97" t="s">
-        <v>14</v>
+        <v>100</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>21</v>
@@ -4410,53 +4426,50 @@
         <v>16</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="G97" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H97" t="s">
+        <v>31</v>
+      </c>
+      <c r="I97" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H97" t="s">
-        <v>31</v>
-      </c>
-      <c r="I97" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" t="s">
-        <v>82</v>
-      </c>
       <c r="B98" t="s">
         <v>14</v>
       </c>
-      <c r="C98" t="s">
-        <v>37</v>
+      <c r="C98" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D98" t="s">
         <v>16</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H98" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
         <v>83</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="H98" t="s">
-        <v>31</v>
-      </c>
-      <c r="I98" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="99" customFormat="1" spans="1:10">
-      <c r="A99" t="s">
-        <v>257</v>
       </c>
       <c r="B99" t="s">
         <v>14</v>
@@ -4468,53 +4481,56 @@
         <v>16</v>
       </c>
       <c r="E99" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="H99" t="s">
         <v>31</v>
       </c>
       <c r="I99" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:10">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="B100" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
+        <v>259</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H100" t="s">
+        <v>31</v>
+      </c>
+      <c r="I100" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:10">
+      <c r="A101" t="s">
         <v>121</v>
       </c>
-      <c r="C100" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E100" t="s">
-        <v>116</v>
-      </c>
-      <c r="G100" t="s">
-        <v>261</v>
-      </c>
-      <c r="H100" t="s">
-        <v>31</v>
-      </c>
-      <c r="I100" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="101" customFormat="1" ht="17" customHeight="1" spans="1:10">
-      <c r="A101" t="s">
-        <v>89</v>
-      </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
         <v>21</v>
@@ -4523,175 +4539,175 @@
         <v>16</v>
       </c>
       <c r="E101" t="s">
+        <v>117</v>
+      </c>
+      <c r="G101" t="s">
         <v>262</v>
       </c>
-      <c r="G101" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="H101" t="s">
         <v>31</v>
       </c>
       <c r="I101" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" t="s">
+        <v>91</v>
+      </c>
+      <c r="C102" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>263</v>
+      </c>
+      <c r="G102" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B102" t="s">
+      <c r="H102" t="s">
+        <v>31</v>
+      </c>
+      <c r="I102" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A103" t="s">
         <v>265</v>
       </c>
-      <c r="C102" t="s">
+      <c r="B103" t="s">
+        <v>266</v>
+      </c>
+      <c r="C103" t="s">
         <v>15</v>
       </c>
-      <c r="D102" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" t="s">
-        <v>262</v>
-      </c>
-      <c r="G102" t="s">
-        <v>266</v>
-      </c>
-      <c r="H102" t="s">
-        <v>31</v>
-      </c>
-      <c r="I102" t="s">
-        <v>93</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
+        <v>263</v>
+      </c>
+      <c r="G103" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="103" customFormat="1" spans="1:10">
-      <c r="A103" t="s">
-        <v>120</v>
-      </c>
-      <c r="B103" t="s">
-        <v>123</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="H103" t="s">
+        <v>31</v>
+      </c>
+      <c r="I103" t="s">
+        <v>94</v>
+      </c>
+      <c r="J103" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" spans="1:10">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" t="s">
+        <v>124</v>
+      </c>
+      <c r="C104" t="s">
         <v>21</v>
       </c>
-      <c r="D103" t="s">
-        <v>16</v>
-      </c>
-      <c r="E103" t="s">
-        <v>116</v>
-      </c>
-      <c r="G103" t="s">
-        <v>268</v>
-      </c>
-      <c r="H103" t="s">
-        <v>31</v>
-      </c>
-      <c r="I103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1" spans="1:10">
-      <c r="A104" t="s">
-        <v>166</v>
-      </c>
-      <c r="B104" t="s">
-        <v>14</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
+        <v>117</v>
+      </c>
+      <c r="G104" t="s">
         <v>269</v>
       </c>
-      <c r="D104" t="s">
-        <v>16</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="H104" t="s">
+        <v>31</v>
+      </c>
+      <c r="I104" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1" spans="1:10">
+      <c r="A105" t="s">
         <v>167</v>
       </c>
-      <c r="F104" t="s">
+      <c r="B105" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" t="s">
+        <v>270</v>
+      </c>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
         <v>168</v>
       </c>
-      <c r="G104" t="s">
-        <v>270</v>
-      </c>
-      <c r="H104" t="s">
-        <v>31</v>
-      </c>
-      <c r="I104" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" t="s">
+      <c r="F105" t="s">
+        <v>169</v>
+      </c>
+      <c r="G105" t="s">
         <v>271</v>
       </c>
-      <c r="B105" t="s">
-        <v>14</v>
-      </c>
-      <c r="C105" t="s">
-        <v>146</v>
-      </c>
-      <c r="D105" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" t="s">
-        <v>147</v>
-      </c>
-      <c r="F105" t="s">
-        <v>272</v>
-      </c>
-      <c r="G105" t="s">
-        <v>273</v>
-      </c>
       <c r="H105" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="I105" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="B106" t="s">
         <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="F106" t="s">
+        <v>273</v>
+      </c>
+      <c r="G106" t="s">
         <v>274</v>
       </c>
-      <c r="G106" t="s">
-        <v>275</v>
-      </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="I106" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D107" t="s">
         <v>16</v>
       </c>
       <c r="E107" t="s">
-        <v>29</v>
+        <v>47</v>
+      </c>
+      <c r="F107" t="s">
+        <v>275</v>
       </c>
       <c r="G107" t="s">
         <v>276</v>
@@ -4700,125 +4716,122 @@
         <v>31</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" t="s">
+        <v>27</v>
+      </c>
+      <c r="B108" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="G108" t="s">
         <v>277</v>
       </c>
-      <c r="B108" t="s">
-        <v>14</v>
-      </c>
-      <c r="C108" t="s">
-        <v>146</v>
-      </c>
-      <c r="D108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="H108" t="s">
+        <v>31</v>
+      </c>
+      <c r="I108" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>278</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" t="s">
         <v>147</v>
       </c>
-      <c r="F108" t="s">
+      <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
         <v>148</v>
       </c>
-      <c r="G108" t="s">
-        <v>278</v>
-      </c>
-      <c r="H108" t="s">
-        <v>150</v>
-      </c>
-      <c r="I108" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B109" t="s">
-        <v>121</v>
-      </c>
-      <c r="C109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D109" t="s">
-        <v>16</v>
-      </c>
-      <c r="E109" t="s">
-        <v>116</v>
-      </c>
       <c r="F109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G109" t="s">
         <v>279</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="I109" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" t="s">
-        <v>277</v>
+      <c r="A110" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D110" t="s">
         <v>16</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>117</v>
+      </c>
+      <c r="F110" t="s">
+        <v>149</v>
       </c>
       <c r="G110" t="s">
         <v>280</v>
       </c>
       <c r="H110" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="I110" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>278</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
+        <v>148</v>
+      </c>
+      <c r="G111" t="s">
+        <v>281</v>
+      </c>
+      <c r="H111" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="111" customFormat="1" spans="1:10">
-      <c r="A111" t="s">
-        <v>281</v>
-      </c>
-      <c r="B111" t="s">
-        <v>14</v>
-      </c>
-      <c r="C111" t="s">
-        <v>37</v>
-      </c>
-      <c r="D111" t="s">
-        <v>16</v>
-      </c>
-      <c r="E111" t="s">
-        <v>282</v>
-      </c>
-      <c r="F111" t="s">
-        <v>283</v>
-      </c>
-      <c r="G111" t="s">
-        <v>284</v>
-      </c>
-      <c r="H111" t="s">
-        <v>31</v>
-      </c>
       <c r="I111" t="s">
-        <v>285</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:10">
       <c r="A112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B112" t="s">
         <v>14</v>
@@ -4830,107 +4843,139 @@
         <v>16</v>
       </c>
       <c r="E112" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F112" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G112" t="s">
+        <v>285</v>
+      </c>
+      <c r="H112" t="s">
+        <v>31</v>
+      </c>
+      <c r="I112" t="s">
         <v>286</v>
-      </c>
-      <c r="H112" t="s">
-        <v>31</v>
-      </c>
-      <c r="I112" t="s">
-        <v>285</v>
-      </c>
-      <c r="J112" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:10">
       <c r="A113" t="s">
+        <v>282</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" t="s">
+        <v>37</v>
+      </c>
+      <c r="D113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>283</v>
+      </c>
+      <c r="F113" t="s">
+        <v>284</v>
+      </c>
+      <c r="G113" t="s">
+        <v>287</v>
+      </c>
+      <c r="H113" t="s">
+        <v>31</v>
+      </c>
+      <c r="I113" t="s">
+        <v>286</v>
+      </c>
+      <c r="J113" t="s">
         <v>288</v>
-      </c>
-      <c r="B113" t="s">
-        <v>14</v>
-      </c>
-      <c r="C113" t="s">
-        <v>191</v>
-      </c>
-      <c r="D113" t="s">
-        <v>289</v>
-      </c>
-      <c r="E113" t="s">
-        <v>290</v>
-      </c>
-      <c r="F113" t="s">
-        <v>291</v>
-      </c>
-      <c r="G113">
-        <v>89789</v>
-      </c>
-      <c r="H113" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:10">
       <c r="A114" t="s">
+        <v>289</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" t="s">
+        <v>290</v>
+      </c>
+      <c r="E114" t="s">
+        <v>291</v>
+      </c>
+      <c r="F114" t="s">
+        <v>292</v>
+      </c>
+      <c r="G114">
+        <v>89789</v>
+      </c>
+      <c r="H114" t="s">
+        <v>31</v>
+      </c>
+      <c r="I114" t="s">
         <v>293</v>
       </c>
-      <c r="B114" t="s">
-        <v>14</v>
-      </c>
-      <c r="C114" t="s">
+    </row>
+    <row r="115" customFormat="1" spans="1:10">
+      <c r="A115" t="s">
         <v>294</v>
       </c>
-      <c r="D114" t="s">
-        <v>16</v>
-      </c>
-      <c r="E114" t="s">
-        <v>116</v>
-      </c>
-      <c r="F114" t="s">
-        <v>291</v>
-      </c>
-      <c r="G114">
+      <c r="B115" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" t="s">
+        <v>295</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>117</v>
+      </c>
+      <c r="F115" t="s">
+        <v>292</v>
+      </c>
+      <c r="G115">
         <v>11223311223</v>
       </c>
-      <c r="H114" t="s">
-        <v>31</v>
-      </c>
-      <c r="I114" t="s">
-        <v>295</v>
-      </c>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" t="s">
-        <v>120</v>
-      </c>
-      <c r="B115" t="s">
-        <v>121</v>
-      </c>
-      <c r="C115" t="s">
-        <v>218</v>
-      </c>
-      <c r="D115" t="s">
-        <v>16</v>
-      </c>
-      <c r="E115" t="s">
-        <v>116</v>
-      </c>
-      <c r="G115" t="s">
-        <v>122</v>
-      </c>
       <c r="H115" t="s">
         <v>31</v>
       </c>
       <c r="I115" t="s">
-        <v>118</v>
+        <v>296</v>
+      </c>
+      <c r="J115" s="1"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>297</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" t="s">
+        <v>47</v>
+      </c>
+      <c r="F116" t="s">
+        <v>292</v>
+      </c>
+      <c r="G116" t="s">
+        <v>298</v>
+      </c>
+      <c r="H116" t="s">
+        <v>31</v>
+      </c>
+      <c r="I116" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
